--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>117808078</v>
       </c>
       <c r="B4" t="n">
-        <v>97744</v>
+        <v>97746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>117808078</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>98263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>117808078</v>
       </c>
       <c r="B4" t="n">
-        <v>98263</v>
+        <v>98265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>117808078</v>
       </c>
       <c r="B4" t="n">
-        <v>98265</v>
+        <v>98273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>117808078</v>
       </c>
       <c r="B4" t="n">
-        <v>98273</v>
+        <v>98276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>117808078</v>
       </c>
       <c r="B4" t="n">
-        <v>98276</v>
+        <v>98278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 11124-2022 artfynd.xlsx
+++ b/artfynd/A 11124-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>117808078</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>98284</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
